--- a/reports/pdf_change_20260828.xlsx
+++ b/reports/pdf_change_20260828.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,20 +38,37 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,16 +77,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00DCE6F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F2"/>
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,11 +114,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -90,10 +143,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 1/7  ·  대기: KoAct, KoAct, TIME, TIME, PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,661억   ·   현금 31억(0.7%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -506,127 +588,973 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 561억   ·   현금 3억(0.5%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>와이씨</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>923560560</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.21%→0.41%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>75→147</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-2260529700</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>3.99%→3.45%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>266→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>2126403500</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2.15%→2.65%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>196→237</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>가온칩스</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-945867000</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>1.76%→1.58%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>175→155</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>2347722000</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>3.85%→4.53%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>143→161</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>한국피아이엠</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-394778800</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.33%→0.22%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>29→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>439504650</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>1.25%→1.34%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>118→127</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-2095080000</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→2.21%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>47→39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>2087377500</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>1.00%→1.44%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>11→16</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-404740700</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.32%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>33→26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-390260000</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>1.21%→1.13%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>72→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-409156800</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>1.44%→1.35%</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>65→61</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-174384600</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.41%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>36→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,895억   ·   현금 12억(0.3%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,642억   ·   현금 33억(1.2%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,237억   ·   현금 30억(1.3%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>496</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>2925904000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.32%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>0→496</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-137</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-8910754000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>13.34%→9.23%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>451→314</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>209</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>2245496000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→2.67%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>341→550</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>삼성에피스홀딩스  (편출)</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-39</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-5038800000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>2.27%→0.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>39→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>179</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>6749374000</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.13%→4.19%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>67→246</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>2214420000</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>3.95%→5.00%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>156→195</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 2억(0.8%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>22982400</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>0.41%→0.50%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>191→229</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-97178400</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>3.16%→2.81%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>300→267</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>38246400</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2.81%→2.95%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>329→345</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-59544000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>7.70%→7.49%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>724→704</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>53082000</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>0.90%→1.09%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>71→86</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-16303680</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>2.78%→2.72%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>858→840</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>32508000</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>0.98%→1.10%</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>59→66</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n"/>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="17" t="n"/>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="17" t="n"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="18">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="G30:K30"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260828.xlsx
+++ b/reports/pdf_change_20260828.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,661억   ·   현금 31억(0.7%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 5종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,661억      당일 2026-08-28  vs  전영업일 2026-08-27      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -967,7 +967,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,895억   ·   현금 12억(0.3%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,895억      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -991,7 +991,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,642억   ·   현금 33억(1.2%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,642억      당일 2026-08-28  vs  전영업일 2026-08-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1015,7 +1015,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,237억   ·   현금 30억(1.3%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,237억      당일 2026-08-28  vs  전영업일 2026-08-27      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1248,7 +1248,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 2억(0.8%)      당일 2026-08-28  vs  전영업일 2026-08-27      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억      당일 2026-08-28  vs  전영업일 2026-08-27      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
